--- a/output/2026-09-07_04_Slovenia_Goriska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-07_04_Slovenia_Goriska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -573,8 +573,6 @@
           <t>Metalworking - Distributore ingrosso flange e raccordi in acciaio al carbonio (EN 1092-1, ANSI B16.5)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Confermato: distributore di flange/raccordi in acciaio carbonio, ISO 9001:2008, attivo dal 2014 (Sloexport, sito ufficiale). Telefono/email non trovati.</t>
@@ -592,7 +590,6 @@
           <t>B.D.V.T. d.o.o.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Nova Gorica</t>
@@ -630,7 +627,6 @@
           <t>GEMOTEHNA, trgovina na drobno in debelo d.o.o. Tolmin</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Tolmin (punto vendita anche a Nova Gorica)</t>
@@ -730,7 +726,6 @@
           <t>(05) 372 80 90</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Confermato su AJPES e come rivenditore autorizzato Bosch Professional (store locator ufficiale Bosch). Telefono/email non riconfermati indipendentemente.</t>
@@ -748,7 +743,6 @@
           <t>INSELT d.o.o. (Inženiring, proizvodnja, elektromehanika, trgovina) Dobrovo</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Dobrovo v Brdih (filiale Nova Gorica - Kromberk)</t>
@@ -813,7 +807,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Confermato: centro tecnico Inpos aperto 2026 presso Supernova Mercator Ajdovščina, primo centro in Primorska (fonti: sito ufficiale, lokalne-ajdovscina.si).</t>
+          <t>Confermato: centro tecnico Inpos aperto 2026 presso Supernova Mercator Ajdovščina, primo centro in Primorska (fonti: sito ufficiale, lokalne-ajdovscina.si). [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -855,7 +849,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Confermato su sito ufficiale e directory locali (Opendi, firmasi.si).</t>
+          <t>Confermato su sito ufficiale e directory locali (Opendi, firmasi.si). [DUPLICATO — vedi anche: 2026-09-05_20_Slovenia_Pomurska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -890,10 +884,9 @@
           <t>+386 (0)51 214 650</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Confermato tramite sito ufficiale; ragione sociale legale del gestore è Vertles d.o.o., P.IVA SI89244052.</t>
+          <t>Confermato tramite sito ufficiale; ragione sociale legale del gestore è Vertles d.o.o., P.IVA SI89244052. [DUPLICATO — vedi anche: 2026-09-07_03_Slovenia_Goriska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -928,7 +921,6 @@
           <t>(05) 333 02 33</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Confermato su Bizi/D&amp;B/rabim.info; commercio all'ingrosso ferramenta e componenti idraulici/termici, vendita guarnizioni e cuscinetti.</t>

--- a/output/2026-09-07_04_Slovenia_Goriska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-07_04_Slovenia_Goriska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
